--- a/skill设计.xlsx
+++ b/skill设计.xlsx
@@ -20,15 +20,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t xml:space="preserve">层级导航</t>
+  </si>
+  <si>
+    <t xml:space="preserve">调用层级导航函数一</t>
+  </si>
+  <si>
+    <t xml:space="preserve">该函数只按照人工经验进行导航，查看（会翻页）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">找到的相关内容合并——
+采用共用的代码</t>
+  </si>
+  <si>
+    <t xml:space="preserve">根据Cortana制订的策略进行必要的过滤——采用共用的代码</t>
+  </si>
+  <si>
+    <t xml:space="preserve">根据任务类型进行其它处理。如下载，则下载。如汇总成列表，则汇总成列表。
+——不同类型的任务可能需要不同的代码，但这部分具有拓展性，用前面的主要工具代码关联不大。现有的基本功能及现有代码（如下载相关的）就可以，以后使用过程中如果有需求，再拓展相关工具。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有可匹配的人工经验</t>
+  </si>
+  <si>
+    <t xml:space="preserve">根据人工经验的指导选择或层级导航，或页面搜索，或层级导航+页面搜索的模式。</t>
+  </si>
   <si>
     <t xml:space="preserve">Cortana理解任务，制订策略</t>
   </si>
   <si>
-    <t xml:space="preserve">有可匹配的人工经验</t>
-  </si>
-  <si>
-    <t xml:space="preserve">确定任务类型，如起始网站，起始页面</t>
+    <t xml:space="preserve">确定任务类型，如是否需要下载，是否需要列表，是否对下载位置有要求，是否对文件名有要求，是否需要对特定文件的标题有特殊要求等等。有一些情况下的默认要求已经写在了skill.md下。
+如，
+不同的医药相关的下载的默认保存位置；
+征求意见稿的撰写说明、意见反馈表需要加上总标题；
+医药等的下载的文件要在文件名前加上发布日期。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">页面搜索</t>
+  </si>
+  <si>
+    <t xml:space="preserve">调用页面搜索函数（共用）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">该函数根据Cortana结合人工经验事先制订的策略（主要是各级关键词，以及关键词的类型，标题，日期？等），进行检索、翻页、查看。</t>
   </si>
   <si>
     <t xml:space="preserve">关键词，不同的关键词分隔</t>
@@ -40,16 +76,22 @@
     <t xml:space="preserve">是否有可匹配的人工经验</t>
   </si>
   <si>
+    <t xml:space="preserve">若有人工经验，Cortana也读取人工经验，整合到一起制订任务策略</t>
+  </si>
+  <si>
     <t xml:space="preserve">寻找搜索栏</t>
   </si>
   <si>
-    <t xml:space="preserve">同步开启基于关键词的搜索</t>
+    <t xml:space="preserve">调用页面搜索函数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以上主要信息构成任务执行策略</t>
   </si>
   <si>
     <t xml:space="preserve">无可匹配的无人工经验</t>
   </si>
   <si>
-    <t xml:space="preserve">层级导航——由Cortana理解每页的内容</t>
+    <t xml:space="preserve">调用层级导航——由Cortana理解每页的内容</t>
   </si>
   <si>
     <t xml:space="preserve">确定与任务相样性强的链接</t>
@@ -130,7 +172,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -139,12 +181,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -164,7 +214,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:G14"/>
+  <dimension ref="A3:K21"/>
   <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.64"/>
@@ -174,82 +224,210 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="5" style="1" width="11.54"/>
   </cols>
   <sheetData>
-    <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="0"/>
+      <c r="D3" s="0"/>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+      <c r="I3" s="0"/>
+      <c r="J3" s="0"/>
+      <c r="K3" s="0"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="0"/>
+      <c r="D4" s="0"/>
+      <c r="E4" s="0"/>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="0"/>
+      <c r="D5" s="0"/>
+      <c r="E5" s="0"/>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+    </row>
+    <row r="6" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" s="2" customFormat="true" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
+      <c r="I7" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3" t="s">
+      <c r="J7" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3" t="s">
+      <c r="K7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="F12" s="1" t="s">
+    <row r="8" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" s="2" customFormat="true" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="C13" s="1" t="s">
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="C10" s="3"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" s="2" customFormat="true" ht="256.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5"/>
+      <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="F14" s="1" t="s">
+      <c r="C11" s="3"/>
+      <c r="E11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="F11" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="G11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" s="2" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5"/>
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" s="2" customFormat="true" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5"/>
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" s="2" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5"/>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" s="2" customFormat="true" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5"/>
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" s="2" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5"/>
+      <c r="B16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+    </row>
+    <row r="17" s="2" customFormat="true" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5"/>
+      <c r="E17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" s="2" customFormat="true" ht="58.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5"/>
+      <c r="C20" s="0"/>
+      <c r="D20" s="0"/>
+      <c r="E20" s="0"/>
+      <c r="F20" s="0"/>
+      <c r="G20" s="0"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5"/>
+      <c r="C21" s="0"/>
+      <c r="D21" s="0"/>
+      <c r="E21" s="0"/>
+      <c r="F21" s="0"/>
+      <c r="G21" s="0"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:A14"/>
+  <mergeCells count="4">
+    <mergeCell ref="I7:I17"/>
+    <mergeCell ref="J7:J17"/>
+    <mergeCell ref="K7:K17"/>
+    <mergeCell ref="A10:A21"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/skill设计.xlsx
+++ b/skill设计.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t xml:space="preserve">层级导航</t>
   </si>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">页面搜索</t>
   </si>
   <si>
-    <t xml:space="preserve">调用页面搜索函数（共用）</t>
+    <t xml:space="preserve">调用页面搜索函数（共用）smart_interact</t>
   </si>
   <si>
     <t xml:space="preserve">该函数根据Cortana结合人工经验事先制订的策略（主要是各级关键词，以及关键词的类型，标题，日期？等），进行检索、翻页、查看。</t>
@@ -73,31 +73,28 @@
     <t xml:space="preserve">是否需要二级或多级过滤；二级或多级过滤策略。</t>
   </si>
   <si>
+    <t xml:space="preserve">寻找搜索栏</t>
+  </si>
+  <si>
     <t xml:space="preserve">是否有可匹配的人工经验</t>
   </si>
   <si>
+    <t xml:space="preserve">无可匹配的无人工经验</t>
+  </si>
+  <si>
+    <t xml:space="preserve">调用层级导航——由Cortana理解每页的内容</t>
+  </si>
+  <si>
     <t xml:space="preserve">若有人工经验，Cortana也读取人工经验，整合到一起制订任务策略</t>
   </si>
   <si>
-    <t xml:space="preserve">寻找搜索栏</t>
-  </si>
-  <si>
-    <t xml:space="preserve">调用页面搜索函数</t>
+    <t xml:space="preserve">确定与任务相样性强的链接</t>
+  </si>
+  <si>
+    <t xml:space="preserve">打开逐级打后由Cortana理解页面内容</t>
   </si>
   <si>
     <t xml:space="preserve">以上主要信息构成任务执行策略</t>
-  </si>
-  <si>
-    <t xml:space="preserve">无可匹配的无人工经验</t>
-  </si>
-  <si>
-    <t xml:space="preserve">调用层级导航——由Cortana理解每页的内容</t>
-  </si>
-  <si>
-    <t xml:space="preserve">确定与任务相样性强的链接</t>
-  </si>
-  <si>
-    <t xml:space="preserve">打开逐级打后由Cortana理解页面内容</t>
   </si>
 </sst>
 </file>
@@ -312,7 +309,7 @@
       <c r="E11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -331,11 +328,19 @@
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" s="2" customFormat="true" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" s="2" customFormat="true" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -343,8 +348,16 @@
     <row r="14" s="2" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -352,13 +365,15 @@
     <row r="15" s="2" customFormat="true" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
       <c r="B15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -367,44 +382,44 @@
     <row r="16" s="2" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
       <c r="B16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
     </row>
-    <row r="17" s="2" customFormat="true" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
-      <c r="E17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="C17" s="0"/>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" s="2" customFormat="true" ht="58.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5"/>
+    <row r="18" s="5" customFormat="true" ht="58.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-    </row>
-    <row r="19" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
